--- a/artfynd/A 17686-2025 artfynd.xlsx
+++ b/artfynd/A 17686-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106032948</v>
+        <v>106032947</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548184.7017865916</v>
+        <v>548159</v>
       </c>
       <c r="R2" t="n">
-        <v>6644810.122522462</v>
+        <v>6644705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,21 +752,11 @@
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,6 +769,21 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Rötbruten granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,37 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106032947</v>
+        <v>106032948</v>
       </c>
       <c r="B3" t="n">
-        <v>89608</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548158.9654662282</v>
+        <v>548184</v>
       </c>
       <c r="R3" t="n">
-        <v>6644704.532360861</v>
+        <v>6644810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,21 +878,11 @@
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,21 +895,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Rötbruten granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,12 +915,7 @@
         <v>106032950</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548297.9579625746</v>
+        <v>548298</v>
       </c>
       <c r="R4" t="n">
-        <v>6644672.261224359</v>
+        <v>6644673</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,19 +989,9 @@
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,12 +1026,7 @@
         <v>106032951</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548297.9579625746</v>
+        <v>548298</v>
       </c>
       <c r="R5" t="n">
-        <v>6644672.261224359</v>
+        <v>6644673</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,19 +1103,9 @@
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,15 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106032953</v>
+        <v>106032952</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1168,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548281.0440453177</v>
+        <v>548287</v>
       </c>
       <c r="R6" t="n">
-        <v>6644583.322316575</v>
+        <v>6644583</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,19 +1218,9 @@
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,15 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106032952</v>
+        <v>106032953</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1283,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1380,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548287.0680523315</v>
+        <v>548281</v>
       </c>
       <c r="R7" t="n">
-        <v>6644583.400940967</v>
+        <v>6644583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,19 +1333,9 @@
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,6 +1365,125 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113315613</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Särvtjärn Ö (knörot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>548298</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6644672</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>U-Fag-0306</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17686-2025 artfynd.xlsx
+++ b/artfynd/A 17686-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032948</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032951</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032952</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032953</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,8 +1519,22 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113315613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>